--- a/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103858</t>
+    <t>20250611134354</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:58+01:00</t>
+    <t>2025-06-11T13:43:54+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250611134354</t>
+    <t>20250616134740</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T13:43:54+01:00</t>
+    <t>2025-06-16T13:47:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134740</t>
+    <t>20250624152101</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:40+01:00</t>
+    <t>2025-06-24T15:21:01+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152101</t>
+    <t>20251216141840</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:01+01:00</t>
+    <t>2025-12-16T14:18:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>C63334</t>
   </si>
   <si>
-    <t>Radiologie interventionnelle</t>
+    <t>imagerie interventionnelle</t>
   </si>
   <si>
     <t>C15747</t>
@@ -148,7 +148,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-ncit</t>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
   </si>
   <si>
     <t>ORG-129</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
@@ -9,12 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141840</t>
+    <t>20260220142105</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:40+01:00</t>
+    <t>2026-02-20T14:21:05+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,76 +96,82 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>C3580</t>
-  </si>
-  <si>
-    <t>métastases osseuses</t>
-  </si>
-  <si>
-    <t>C3303</t>
-  </si>
-  <si>
-    <t>douleur</t>
-  </si>
-  <si>
-    <t>C15252</t>
-  </si>
-  <si>
-    <t>soins palliatifs</t>
-  </si>
-  <si>
-    <t>C63334</t>
+    <t>C79.5</t>
+  </si>
+  <si>
+    <t>Tumeur maligne secondaire des os et de la moelle osseuse</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/sid/icd-10</t>
+  </si>
+  <si>
+    <t>C16832</t>
+  </si>
+  <si>
+    <t>oncologie médicale</t>
+  </si>
+  <si>
+    <t>C7201</t>
+  </si>
+  <si>
+    <t>tumeur rare</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
+  </si>
+  <si>
+    <t>ORG-129</t>
+  </si>
+  <si>
+    <t>Oncogénétique</t>
+  </si>
+  <si>
+    <t>ORG-130</t>
+  </si>
+  <si>
+    <t>Oncogériatrie</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>410240006</t>
+  </si>
+  <si>
+    <t>prise en charge du traitement de la douleur</t>
+  </si>
+  <si>
+    <t>103735009</t>
+  </si>
+  <si>
+    <t>soin palliatif</t>
+  </si>
+  <si>
+    <t>258174001</t>
   </si>
   <si>
     <t>imagerie interventionnelle</t>
   </si>
   <si>
-    <t>C15747</t>
-  </si>
-  <si>
-    <t>soins de support</t>
-  </si>
-  <si>
-    <t>C16832</t>
-  </si>
-  <si>
-    <t>oncologie médicale</t>
-  </si>
-  <si>
-    <t>C71326</t>
-  </si>
-  <si>
-    <t>préservation de la fertilité</t>
-  </si>
-  <si>
-    <t>C7201</t>
-  </si>
-  <si>
-    <t>tumeur rare</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
-  </si>
-  <si>
-    <t>ORG-129</t>
-  </si>
-  <si>
-    <t>Oncogénétique</t>
-  </si>
-  <si>
-    <t>ORG-130</t>
-  </si>
-  <si>
-    <t>Oncogériatrie</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+    <t>243114000</t>
+  </si>
+  <si>
+    <t>soin de support</t>
+  </si>
+  <si>
+    <t>702596005</t>
+  </si>
+  <si>
+    <t>procédure de préservation de la fertilité</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -419,7 +427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -447,71 +455,15 @@
         <v>28</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -538,34 +490,166 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
         <v>43</v>
       </c>
+      <c r="B3" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>47</v>
+      </c>
       <c r="B5" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
         <v>49</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
@@ -9,14 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
-    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -39,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142105</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:05+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,10 +94,28 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>C79.5</t>
-  </si>
-  <si>
-    <t>Tumeur maligne secondaire des os et de la moelle osseuse</t>
+    <t>ORG-225</t>
+  </si>
+  <si>
+    <t>RCP Métastase osseuse</t>
+  </si>
+  <si>
+    <t>ORG-129</t>
+  </si>
+  <si>
+    <t>Oncogénétique</t>
+  </si>
+  <si>
+    <t>ORG-130</t>
+  </si>
+  <si>
+    <t>Oncogériatrie</t>
+  </si>
+  <si>
+    <t>ORG-226</t>
+  </si>
+  <si>
+    <t>RCP Cancers rares</t>
   </si>
   <si>
     <t/>
@@ -108,61 +124,37 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/sid/icd-10</t>
-  </si>
-  <si>
-    <t>C16832</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>410240006</t>
+  </si>
+  <si>
+    <t>prise en charge du traitement de la douleur</t>
+  </si>
+  <si>
+    <t>103735009</t>
+  </si>
+  <si>
+    <t>soin palliatif</t>
+  </si>
+  <si>
+    <t>258174001</t>
+  </si>
+  <si>
+    <t>imagerie interventionnelle</t>
+  </si>
+  <si>
+    <t>243114000</t>
+  </si>
+  <si>
+    <t>soin de support</t>
+  </si>
+  <si>
+    <t>394593009</t>
   </si>
   <si>
     <t>oncologie médicale</t>
-  </si>
-  <si>
-    <t>C7201</t>
-  </si>
-  <si>
-    <t>tumeur rare</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
-  </si>
-  <si>
-    <t>ORG-129</t>
-  </si>
-  <si>
-    <t>Oncogénétique</t>
-  </si>
-  <si>
-    <t>ORG-130</t>
-  </si>
-  <si>
-    <t>Oncogériatrie</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
-  </si>
-  <si>
-    <t>410240006</t>
-  </si>
-  <si>
-    <t>prise en charge du traitement de la douleur</t>
-  </si>
-  <si>
-    <t>103735009</t>
-  </si>
-  <si>
-    <t>soin palliatif</t>
-  </si>
-  <si>
-    <t>258174001</t>
-  </si>
-  <si>
-    <t>imagerie interventionnelle</t>
-  </si>
-  <si>
-    <t>243114000</t>
-  </si>
-  <si>
-    <t>soin de support</t>
   </si>
   <si>
     <t>702596005</t>
@@ -427,7 +419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -455,15 +447,39 @@
         <v>28</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -473,7 +489,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -490,166 +506,66 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B3" t="s" s="2">
         <v>44</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>51</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-traitement-soins-frcp-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150251</t>
+    <t>20260619134043</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:51+01:00</t>
+    <t>2026-06-19T13:40:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
